--- a/inst/dados_premissas/2025/custos.xlsx
+++ b/inst/dados_premissas/2025/custos.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E6E0D1-14F2-40A6-BDE5-42129C009205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{87E96AAD-C3DA-4E91-8719-171D3DD1A059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FB34793-3978-4BA5-8C7C-1CD8FEC72FD8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -558,7 +558,7 @@
         <v>2026</v>
       </c>
       <c r="C15" s="1">
-        <v>2.9919687967293664</v>
+        <v>3.0830254482974966</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -569,7 +569,7 @@
         <v>2027</v>
       </c>
       <c r="C16" s="1">
-        <v>2.9058000953835608</v>
+        <v>2.9942343153865285</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -580,7 +580,7 @@
         <v>2028</v>
       </c>
       <c r="C17" s="1">
-        <v>2.8221130526365141</v>
+        <v>2.9080003671033965</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -591,7 +591,7 @@
         <v>2029</v>
       </c>
       <c r="C18" s="1">
-        <v>2.7408361967205823</v>
+        <v>2.8242499565308186</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -602,7 +602,7 @@
         <v>2030</v>
       </c>
       <c r="C19" s="1">
-        <v>2.6619001142550296</v>
+        <v>2.742911557782731</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -613,7 +613,7 @@
         <v>2031</v>
       </c>
       <c r="C20" s="1">
-        <v>2.6226839345682817</v>
+        <v>2.702501885030991</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -624,7 +624,7 @@
         <v>2032</v>
       </c>
       <c r="C21" s="1">
-        <v>2.5840455033631495</v>
+        <v>2.6626875437791928</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -635,7 +635,7 @@
         <v>2033</v>
       </c>
       <c r="C22" s="1">
-        <v>2.5459763090173722</v>
+        <v>2.6234597633650005</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -646,7 +646,7 @@
         <v>2034</v>
       </c>
       <c r="C23" s="1">
-        <v>2.5084679653053201</v>
+        <v>2.5848099023389914</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -657,7 +657,7 @@
         <v>2035</v>
       </c>
       <c r="C24" s="1">
-        <v>2.4715122095506024</v>
+        <v>2.5467294465610406</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -668,7 +668,7 @@
         <v>2036</v>
       </c>
       <c r="C25" s="1">
-        <v>2.4351009008058893</v>
+        <v>2.5092100073247492</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -679,7 +679,7 @@
         <v>2037</v>
       </c>
       <c r="C26" s="1">
-        <v>2.3992260180595504</v>
+        <v>2.4722433195095035</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -690,7 +690,7 @@
         <v>2038</v>
       </c>
       <c r="C27" s="1">
-        <v>2.3638796584687154</v>
+        <v>2.4358212397597607</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -701,7 +701,7 @@
         <v>2039</v>
       </c>
       <c r="C28" s="1">
-        <v>2.3290540356183627</v>
+        <v>2.3999357446911569</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -712,7 +712,7 @@
         <v>2040</v>
       </c>
       <c r="C29" s="1">
-        <v>2.2947414778060584</v>
+        <v>2.3645789291230428</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -723,7 +723,7 @@
         <v>2041</v>
       </c>
       <c r="C30" s="1">
-        <v>2.2643031511663674</v>
+        <v>2.3332142518789682</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -734,7 +734,7 @@
         <v>2042</v>
       </c>
       <c r="C31" s="1">
-        <v>2.2342685701065532</v>
+        <v>2.3022656076826844</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -745,7 +745,7 @@
         <v>2043</v>
       </c>
       <c r="C32" s="1">
-        <v>2.2046323791911746</v>
+        <v>2.2717274781130863</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -756,7 +756,7 @@
         <v>2044</v>
       </c>
       <c r="C33" s="1">
-        <v>2.1753892940213286</v>
+        <v>2.2415944179475122</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -767,7 +767,7 @@
         <v>2045</v>
       </c>
       <c r="C34" s="1">
-        <v>2.146534100292397</v>
+        <v>2.2118610541908121</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -778,7 +778,7 @@
         <v>2046</v>
       </c>
       <c r="C35" s="1">
-        <v>2.1180616528642875</v>
+        <v>2.1825220851172937</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -789,7 +789,7 @@
         <v>2047</v>
       </c>
       <c r="C36" s="1">
-        <v>2.0899668748440088</v>
+        <v>2.1535722793253775</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -800,7 +800,7 @@
         <v>2048</v>
       </c>
       <c r="C37" s="1">
-        <v>2.0622447566804163</v>
+        <v>2.125006474804791</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -811,7 +811,7 @@
         <v>2049</v>
       </c>
       <c r="C38" s="1">
-        <v>2.0348903552709632</v>
+        <v>2.0968195780161354</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -822,7 +822,7 @@
         <v>2050</v>
       </c>
       <c r="C39" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -833,7 +833,7 @@
         <v>2051</v>
       </c>
       <c r="C40" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -844,7 +844,7 @@
         <v>2052</v>
       </c>
       <c r="C41" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -855,7 +855,7 @@
         <v>2053</v>
       </c>
       <c r="C42" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -866,7 +866,7 @@
         <v>2054</v>
       </c>
       <c r="C43" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>2055</v>
       </c>
       <c r="C44" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -888,7 +888,7 @@
         <v>2056</v>
       </c>
       <c r="C45" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -899,7 +899,7 @@
         <v>2057</v>
       </c>
       <c r="C46" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -910,7 +910,7 @@
         <v>2058</v>
       </c>
       <c r="C47" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -921,7 +921,7 @@
         <v>2059</v>
       </c>
       <c r="C48" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -932,7 +932,7 @@
         <v>2060</v>
       </c>
       <c r="C49" s="1">
-        <v>2.0078987930803009</v>
+        <v>2.0690065629826622</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -1086,7 +1086,7 @@
         <v>2026</v>
       </c>
       <c r="C63" s="1">
-        <v>2.3333431349827025</v>
+        <v>2.3727753455377911</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -1097,7 +1097,7 @@
         <v>2027</v>
       </c>
       <c r="C64" s="1">
-        <v>2.2661428526952005</v>
+        <v>2.3044394155863026</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -1108,7 +1108,7 @@
         <v>2028</v>
       </c>
       <c r="C65" s="1">
-        <v>2.2008779385375785</v>
+        <v>2.2380715604174171</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -1119,7 +1119,7 @@
         <v>2029</v>
       </c>
       <c r="C66" s="1">
-        <v>2.1374926539076959</v>
+        <v>2.1736150994773955</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -1130,7 +1130,7 @@
         <v>2030</v>
       </c>
       <c r="C67" s="1">
-        <v>2.0759328654751541</v>
+        <v>2.1110149846124466</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -1141,7 +1141,7 @@
         <v>2031</v>
       </c>
       <c r="C68" s="1">
-        <v>2.0453493902222211</v>
+        <v>2.0799146655153313</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -1152,7 +1152,7 @@
         <v>2032</v>
       </c>
       <c r="C69" s="1">
-        <v>2.0152164829881785</v>
+        <v>2.0492725287878311</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1163,7 +1163,7 @@
         <v>2033</v>
       </c>
       <c r="C70" s="1">
-        <v>1.9855275058243311</v>
+        <v>2.0190818243035831</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -1174,7 +1174,7 @@
         <v>2034</v>
       </c>
       <c r="C71" s="1">
-        <v>1.9562759185749055</v>
+        <v>1.9893359013817924</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -1185,7 +1185,7 @@
         <v>2035</v>
       </c>
       <c r="C72" s="1">
-        <v>1.9274552774363249</v>
+        <v>1.9600282073221602</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -1196,7 +1196,7 @@
         <v>2036</v>
       </c>
       <c r="C73" s="1">
-        <v>1.8990592335377103</v>
+        <v>1.9311522859613952</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -1207,7 +1207,7 @@
         <v>2037</v>
       </c>
       <c r="C74" s="1">
-        <v>1.871081531542294</v>
+        <v>1.9027017762509921</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -1218,7 +1218,7 @@
         <v>2038</v>
       </c>
       <c r="C75" s="1">
-        <v>1.8435160082694371</v>
+        <v>1.8746704108559629</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -1229,7 +1229,7 @@
         <v>2039</v>
       </c>
       <c r="C76" s="1">
-        <v>1.816356591336949</v>
+        <v>1.8470520147742107</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -1240,7 +1240,7 @@
         <v>2040</v>
       </c>
       <c r="C77" s="1">
-        <v>1.7895972978234083</v>
+        <v>1.8198405039762457</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -1251,7 +1251,7 @@
         <v>2041</v>
       </c>
       <c r="C78" s="1">
-        <v>1.765859396351066</v>
+        <v>1.7957014450766224</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -1262,7 +1262,7 @@
         <v>2042</v>
       </c>
       <c r="C79" s="1">
-        <v>1.7424363634622848</v>
+        <v>1.7718825758657584</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -1273,7 +1273,7 @@
         <v>2043</v>
       </c>
       <c r="C80" s="1">
-        <v>1.7193240226200182</v>
+        <v>1.7483796492254366</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -1284,7 +1284,7 @@
         <v>2044</v>
       </c>
       <c r="C81" s="1">
-        <v>1.6965182526864</v>
+        <v>1.7251884743728374</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -1295,7 +1295,7 @@
         <v>2045</v>
       </c>
       <c r="C82" s="1">
-        <v>1.6740149871879102</v>
+        <v>1.7023049161132831</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -1306,7 +1306,7 @@
         <v>2046</v>
       </c>
       <c r="C83" s="1">
-        <v>1.6518102135902848</v>
+        <v>1.6797248941028964</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -1317,7 +1317,7 @@
         <v>2047</v>
       </c>
       <c r="C84" s="1">
-        <v>1.6298999725830456</v>
+        <v>1.6574443821210383</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -1328,7 +1328,7 @@
         <v>2048</v>
       </c>
       <c r="C85" s="1">
-        <v>1.6082803573735196</v>
+        <v>1.6354594073523969</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -1339,7 +1339,7 @@
         <v>2049</v>
       </c>
       <c r="C86" s="1">
-        <v>1.5869475129902222</v>
+        <v>1.6137660496785984</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -1350,7 +1350,7 @@
         <v>2050</v>
       </c>
       <c r="C87" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -1361,7 +1361,7 @@
         <v>2051</v>
       </c>
       <c r="C88" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -1372,7 +1372,7 @@
         <v>2052</v>
       </c>
       <c r="C89" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -1383,7 +1383,7 @@
         <v>2053</v>
       </c>
       <c r="C90" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -1394,7 +1394,7 @@
         <v>2054</v>
       </c>
       <c r="C91" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -1405,7 +1405,7 @@
         <v>2055</v>
       </c>
       <c r="C92" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -1416,7 +1416,7 @@
         <v>2056</v>
       </c>
       <c r="C93" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -1427,7 +1427,7 @@
         <v>2057</v>
       </c>
       <c r="C94" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -1438,7 +1438,7 @@
         <v>2058</v>
       </c>
       <c r="C95" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -1449,7 +1449,7 @@
         <v>2059</v>
       </c>
       <c r="C96" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -1460,7 +1460,7 @@
         <v>2060</v>
       </c>
       <c r="C97" s="1">
-        <v>1.5658976355954823</v>
+        <v>1.5923604409792151</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -1614,7 +1614,7 @@
         <v>2026</v>
       </c>
       <c r="C111" s="1">
-        <v>2.4366381959822081</v>
+        <v>2.4771970411245854</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -1625,7 +1625,7 @@
         <v>2027</v>
       </c>
       <c r="C112" s="1">
-        <v>2.3664630159379203</v>
+        <v>2.4058537663401971</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
@@ -1636,7 +1636,7 @@
         <v>2028</v>
       </c>
       <c r="C113" s="1">
-        <v>2.2983088810789081</v>
+        <v>2.3365651778695993</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -1647,7 +1647,7 @@
         <v>2029</v>
       </c>
       <c r="C114" s="1">
-        <v>2.2321175853038353</v>
+        <v>2.2692721007469547</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
@@ -1658,7 +1658,7 @@
         <v>2030</v>
       </c>
       <c r="C115" s="1">
-        <v>2.1678325988470846</v>
+        <v>2.2039170642454424</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
@@ -1669,7 +1669,7 @@
         <v>2031</v>
       </c>
       <c r="C116" s="1">
-        <v>2.1358952198778631</v>
+        <v>2.1714480744650624</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -1680,7 +1680,7 @@
         <v>2032</v>
       </c>
       <c r="C117" s="1">
-        <v>2.104428355179885</v>
+        <v>2.1394574308595278</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -1691,7 +1691,7 @@
         <v>2033</v>
       </c>
       <c r="C118" s="1">
-        <v>2.0734250729482682</v>
+        <v>2.1079380862412131</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -1702,7 +1702,7 @@
         <v>2034</v>
       </c>
       <c r="C119" s="1">
-        <v>2.0428785435002603</v>
+        <v>2.0768830972444867</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
@@ -1713,7 +1713,7 @@
         <v>2035</v>
       </c>
       <c r="C120" s="1">
-        <v>2.0127820377707324</v>
+        <v>2.0462856227961628</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -1724,7 +1724,7 @@
         <v>2036</v>
       </c>
       <c r="C121" s="1">
-        <v>1.9831289258298412</v>
+        <v>2.0161389226084885</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
@@ -1735,7 +1735,7 @@
         <v>2037</v>
       </c>
       <c r="C122" s="1">
-        <v>1.9539126754225282</v>
+        <v>1.9864363556943321</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
@@ -1746,7 +1746,7 @@
         <v>2038</v>
       </c>
       <c r="C123" s="1">
-        <v>1.9251268505295351</v>
+        <v>1.9571713789042473</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -1757,7 +1757,7 @@
         <v>2039</v>
       </c>
       <c r="C124" s="1">
-        <v>1.8967651099496194</v>
+        <v>1.9283375454850886</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -1768,7 +1768,7 @@
         <v>2040</v>
       </c>
       <c r="C125" s="1">
-        <v>1.8688212059026581</v>
+        <v>1.8999285036598625</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -1779,7 +1779,7 @@
         <v>2041</v>
       </c>
       <c r="C126" s="1">
-        <v>1.8440324482815462</v>
+        <v>1.8747271269706902</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
@@ -1790,7 +1790,7 @@
         <v>2042</v>
       </c>
       <c r="C127" s="1">
-        <v>1.8195724982009618</v>
+        <v>1.8498600309588202</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -1801,7 +1801,7 @@
         <v>2043</v>
       </c>
       <c r="C128" s="1">
-        <v>1.7954369942322135</v>
+        <v>1.8253227815977868</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
@@ -1812,7 +1812,7 @@
         <v>2044</v>
       </c>
       <c r="C129" s="1">
-        <v>1.7716216327982646</v>
+        <v>1.8011110036757429</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
@@ -1823,7 +1823,7 @@
         <v>2045</v>
       </c>
       <c r="C130" s="1">
-        <v>1.7481221674063665</v>
+        <v>1.7772203800153215</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -1834,7 +1834,7 @@
         <v>2046</v>
       </c>
       <c r="C131" s="1">
-        <v>1.724934407890871</v>
+        <v>1.7536466507038428</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -1845,7 +1845,7 @@
         <v>2047</v>
       </c>
       <c r="C132" s="1">
-        <v>1.7020542196660857</v>
+        <v>1.7303856123337353</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -1856,7 +1856,7 @@
         <v>2048</v>
       </c>
       <c r="C133" s="1">
-        <v>1.6794775229890408</v>
+        <v>1.707433117253029</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
@@ -1867,7 +1867,7 @@
         <v>2049</v>
       </c>
       <c r="C134" s="1">
-        <v>1.6572002922320344</v>
+        <v>1.6847850728257927</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -1878,7 +1878,7 @@
         <v>2050</v>
       </c>
       <c r="C135" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
@@ -1889,7 +1889,7 @@
         <v>2051</v>
       </c>
       <c r="C136" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
@@ -1900,7 +1900,7 @@
         <v>2052</v>
       </c>
       <c r="C137" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -1911,7 +1911,7 @@
         <v>2053</v>
       </c>
       <c r="C138" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -1922,7 +1922,7 @@
         <v>2054</v>
       </c>
       <c r="C139" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -1933,7 +1933,7 @@
         <v>2055</v>
       </c>
       <c r="C140" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
@@ -1944,7 +1944,7 @@
         <v>2056</v>
       </c>
       <c r="C141" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -1955,7 +1955,7 @@
         <v>2057</v>
       </c>
       <c r="C142" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
@@ -1966,7 +1966,7 @@
         <v>2058</v>
       </c>
       <c r="C143" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
@@ -1977,7 +1977,7 @@
         <v>2059</v>
       </c>
       <c r="C144" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -1988,7 +1988,7 @@
         <v>2060</v>
       </c>
       <c r="C145" s="1">
-        <v>1.6352185551648259</v>
+        <v>1.6624374407023796</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -2142,7 +2142,7 @@
         <v>2026</v>
       </c>
       <c r="C159" s="1">
-        <v>3.0096461959822083</v>
+        <v>3.0502050411245856</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -2153,7 +2153,7 @@
         <v>2027</v>
       </c>
       <c r="C160" s="1">
-        <v>2.9229683855379207</v>
+        <v>2.9623591359401975</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
@@ -2164,7 +2164,7 @@
         <v>2028</v>
       </c>
       <c r="C161" s="1">
-        <v>2.8387868960344282</v>
+        <v>2.8770431928251199</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
@@ -2175,7 +2175,7 @@
         <v>2029</v>
       </c>
       <c r="C162" s="1">
-        <v>2.7570298334286365</v>
+        <v>2.7941843488717564</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -2186,7 +2186,7 @@
         <v>2030</v>
       </c>
       <c r="C163" s="1">
-        <v>2.6776273742258918</v>
+        <v>2.7137118396242497</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
@@ -2197,7 +2197,7 @@
         <v>2031</v>
       </c>
       <c r="C164" s="1">
-        <v>2.6381794942399126</v>
+        <v>2.6737323488271119</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
@@ -2208,7 +2208,7 @@
         <v>2032</v>
       </c>
       <c r="C165" s="1">
-        <v>2.5993127762372499</v>
+        <v>2.6343418519168931</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -2219,7 +2219,7 @@
         <v>2033</v>
       </c>
       <c r="C166" s="1">
-        <v>2.5610186583065677</v>
+        <v>2.5955316715995127</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -2230,7 +2230,7 @@
         <v>2034</v>
       </c>
       <c r="C167" s="1">
-        <v>2.5232887046740395</v>
+        <v>2.5572932584182664</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -2241,7 +2241,7 @@
         <v>2035</v>
       </c>
       <c r="C168" s="1">
-        <v>2.4861146038450412</v>
+        <v>2.5196181888704725</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
@@ -2252,7 +2252,7 @@
         <v>2036</v>
       </c>
       <c r="C169" s="1">
-        <v>2.4494881667732202</v>
+        <v>2.4824981635518681</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -2263,7 +2263,7 @@
         <v>2037</v>
       </c>
       <c r="C170" s="1">
-        <v>2.4134013250565376</v>
+        <v>2.4459250053283421</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
@@ -2274,7 +2274,7 @@
         <v>2038</v>
       </c>
       <c r="C171" s="1">
-        <v>2.3778461291598876</v>
+        <v>2.4098906575346009</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
@@ -2285,7 +2285,7 @@
         <v>2039</v>
       </c>
       <c r="C172" s="1">
-        <v>2.3428147466639033</v>
+        <v>2.3743871821993738</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
@@ -2296,7 +2296,7 @@
         <v>2040</v>
       </c>
       <c r="C173" s="1">
-        <v>2.3082994605395601</v>
+        <v>2.3394067582967661</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -2307,7 +2307,7 @@
         <v>2041</v>
       </c>
       <c r="C174" s="1">
-        <v>2.2776812956431378</v>
+        <v>2.3083759743322831</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
@@ -2318,7 +2318,7 @@
         <v>2042</v>
       </c>
       <c r="C175" s="1">
-        <v>2.2474692617698562</v>
+        <v>2.2777567945277162</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
@@ -2329,7 +2329,7 @@
         <v>2043</v>
       </c>
       <c r="C176" s="1">
-        <v>2.2176579718428444</v>
+        <v>2.2475437592084191</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
@@ -2340,7 +2340,7 @@
         <v>2044</v>
       </c>
       <c r="C177" s="1">
-        <v>2.188242110241474</v>
+        <v>2.2177314811189537</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
@@ -2351,7 +2351,7 @@
         <v>2045</v>
       </c>
       <c r="C178" s="1">
-        <v>2.1592164318535376</v>
+        <v>2.1883146444624937</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
@@ -2362,7 +2362,7 @@
         <v>2046</v>
       </c>
       <c r="C179" s="1">
-        <v>2.1305757611399971</v>
+        <v>2.1592880039529705</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -2373,7 +2373,7 @@
         <v>2047</v>
       </c>
       <c r="C180" s="1">
-        <v>2.1023149912121402</v>
+        <v>2.1306463838797911</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -2384,7 +2384,7 @@
         <v>2048</v>
       </c>
       <c r="C181" s="1">
-        <v>2.0744290829209744</v>
+        <v>2.1023846771849635</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
@@ -2395,7 +2395,7 @@
         <v>2049</v>
       </c>
       <c r="C182" s="1">
-        <v>2.0469130639587023</v>
+        <v>2.0744978445524618</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
@@ -2406,7 +2406,7 @@
         <v>2050</v>
       </c>
       <c r="C183" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
@@ -2417,7 +2417,7 @@
         <v>2051</v>
       </c>
       <c r="C184" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
@@ -2428,7 +2428,7 @@
         <v>2052</v>
       </c>
       <c r="C185" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
@@ -2439,7 +2439,7 @@
         <v>2053</v>
       </c>
       <c r="C186" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -2450,7 +2450,7 @@
         <v>2054</v>
       </c>
       <c r="C187" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
@@ -2461,7 +2461,7 @@
         <v>2055</v>
       </c>
       <c r="C188" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
@@ -2472,7 +2472,7 @@
         <v>2056</v>
       </c>
       <c r="C189" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
@@ -2483,7 +2483,7 @@
         <v>2057</v>
       </c>
       <c r="C190" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
@@ -2494,7 +2494,7 @@
         <v>2058</v>
       </c>
       <c r="C191" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
@@ -2505,7 +2505,7 @@
         <v>2059</v>
       </c>
       <c r="C192" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
@@ -2516,7 +2516,7 @@
         <v>2060</v>
       </c>
       <c r="C193" s="1">
-        <v>2.0197620279721153</v>
+        <v>2.0469809135096702</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
@@ -2675,7 +2675,7 @@
         <v>2026</v>
       </c>
       <c r="C207" s="1">
-        <v>2.4688617264819612</v>
+        <v>2.5099838889179829</v>
       </c>
       <c r="E207" s="1"/>
     </row>
@@ -2687,7 +2687,7 @@
         <v>2027</v>
       </c>
       <c r="C208" s="1">
-        <v>2.3977585087592805</v>
+        <v>2.4376963529171447</v>
       </c>
       <c r="E208" s="1"/>
     </row>
@@ -2699,7 +2699,7 @@
         <v>2028</v>
       </c>
       <c r="C209" s="1">
-        <v>2.328703063707013</v>
+        <v>2.3674906979531309</v>
       </c>
       <c r="E209" s="1"/>
     </row>
@@ -2711,7 +2711,7 @@
         <v>2029</v>
       </c>
       <c r="C210" s="1">
-        <v>2.261636415472251</v>
+        <v>2.2993069658520806</v>
       </c>
       <c r="E210" s="1"/>
     </row>
@@ -2723,7 +2723,7 @@
         <v>2030</v>
       </c>
       <c r="C211" s="1">
-        <v>2.19650128670665</v>
+        <v>2.2330869252355408</v>
       </c>
       <c r="E211" s="1"/>
     </row>
@@ -2735,7 +2735,7 @@
         <v>2031</v>
       </c>
       <c r="C212" s="1">
-        <v>2.1641415491340901</v>
+        <v>2.2001881933683336</v>
       </c>
       <c r="E212" s="1"/>
     </row>
@@ -2747,7 +2747,7 @@
         <v>2032</v>
       </c>
       <c r="C213" s="1">
-        <v>2.1322585481890486</v>
+        <v>2.1677741388086864</v>
       </c>
       <c r="E213" s="1"/>
     </row>
@@ -2759,7 +2759,7 @@
         <v>2033</v>
       </c>
       <c r="C214" s="1">
-        <v>2.100845260396397</v>
+        <v>2.1358376210961882</v>
       </c>
       <c r="E214" s="1"/>
     </row>
@@ -2771,7 +2771,7 @@
         <v>2034</v>
       </c>
       <c r="C215" s="1">
-        <v>2.0698947657536575</v>
+        <v>2.1043716049665542</v>
       </c>
       <c r="E215" s="1"/>
     </row>
@@ -2783,7 +2783,7 @@
         <v>2035</v>
       </c>
       <c r="C216" s="1">
-        <v>2.0394002462066041</v>
+        <v>2.0733691588018326</v>
       </c>
       <c r="E216" s="1"/>
     </row>
@@ -2795,7 +2795,7 @@
         <v>2036</v>
       </c>
       <c r="C217" s="1">
-        <v>2.0093549841473179</v>
+        <v>2.042823453103447</v>
       </c>
       <c r="E217" s="1"/>
     </row>
@@ -2807,7 +2807,7 @@
         <v>2037</v>
       </c>
       <c r="C218" s="1">
-        <v>1.9797523609343743</v>
+        <v>2.0127277589877317</v>
       </c>
       <c r="E218" s="1"/>
     </row>
@@ -2819,7 +2819,7 @@
         <v>2038</v>
       </c>
       <c r="C219" s="1">
-        <v>1.9505858554348268</v>
+        <v>1.9830754467036331</v>
       </c>
       <c r="E219" s="1"/>
     </row>
@@ -2831,7 +2831,7 @@
         <v>2039</v>
       </c>
       <c r="C220" s="1">
-        <v>1.9218490425876742</v>
+        <v>1.9538599841722482</v>
       </c>
       <c r="E220" s="1"/>
     </row>
@@ -2843,7 +2843,7 @@
         <v>2040</v>
       </c>
       <c r="C221" s="1">
-        <v>1.8935355919884902</v>
+        <v>1.9250749355478789</v>
       </c>
       <c r="E221" s="1"/>
     </row>
@@ -2855,7 +2855,7 @@
         <v>2041</v>
       </c>
       <c r="C222" s="1">
-        <v>1.8684190133192753</v>
+        <v>1.8995400069902137</v>
       </c>
       <c r="E222" s="1"/>
     </row>
@@ -2867,7 +2867,7 @@
         <v>2042</v>
       </c>
       <c r="C223" s="1">
-        <v>1.8436355905340669</v>
+        <v>1.8743437834691188</v>
       </c>
       <c r="E223" s="1"/>
     </row>
@@ -2879,7 +2879,7 @@
         <v>2043</v>
       </c>
       <c r="C224" s="1">
-        <v>1.8191809045260867</v>
+        <v>1.8494817722717383</v>
       </c>
       <c r="E224" s="1"/>
     </row>
@@ -2891,7 +2891,7 @@
         <v>2044</v>
       </c>
       <c r="C225" s="1">
-        <v>1.7950505948052748</v>
+        <v>1.8249495402782745</v>
       </c>
       <c r="E225" s="1"/>
     </row>
@@ -2903,7 +2903,7 @@
         <v>2045</v>
       </c>
       <c r="C226" s="1">
-        <v>1.7712403587207757</v>
+        <v>1.8007427131715223</v>
       </c>
       <c r="E226" s="1"/>
     </row>
@@ -2915,7 +2915,7 @@
         <v>2046</v>
       </c>
       <c r="C227" s="1">
-        <v>1.7477459506937365</v>
+        <v>1.7768569746568892</v>
       </c>
       <c r="E227" s="1"/>
     </row>
@@ -2927,7 +2927,7 @@
         <v>2047</v>
       </c>
       <c r="C228" s="1">
-        <v>1.7245631814602824</v>
+        <v>1.7532880656927612</v>
       </c>
       <c r="E228" s="1"/>
     </row>
@@ -2939,7 +2939,7 @@
         <v>2048</v>
       </c>
       <c r="C229" s="1">
-        <v>1.7016879173245332</v>
+        <v>1.7300317837310775</v>
       </c>
       <c r="E229" s="1"/>
     </row>
@@ -2951,7 +2951,7 @@
         <v>2049</v>
       </c>
       <c r="C230" s="1">
-        <v>1.6791160794215285</v>
+        <v>1.7070839819679786</v>
       </c>
       <c r="E230" s="1"/>
     </row>
@@ -2963,7 +2963,7 @@
         <v>2050</v>
       </c>
       <c r="C231" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
       <c r="E231" s="1"/>
     </row>
@@ -2975,7 +2975,7 @@
         <v>2051</v>
       </c>
       <c r="C232" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
@@ -2986,7 +2986,7 @@
         <v>2052</v>
       </c>
       <c r="C233" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
@@ -2997,7 +2997,7 @@
         <v>2053</v>
       </c>
       <c r="C234" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
@@ -3008,7 +3008,7 @@
         <v>2054</v>
       </c>
       <c r="C235" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
@@ -3019,7 +3019,7 @@
         <v>2055</v>
       </c>
       <c r="C236" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
@@ -3030,7 +3030,7 @@
         <v>2056</v>
       </c>
       <c r="C237" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
@@ -3041,7 +3041,7 @@
         <v>2057</v>
       </c>
       <c r="C238" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
@@ -3052,7 +3052,7 @@
         <v>2058</v>
       </c>
       <c r="C239" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
@@ -3063,7 +3063,7 @@
         <v>2059</v>
       </c>
       <c r="C240" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.3">
@@ -3074,11 +3074,16 @@
         <v>2060</v>
       </c>
       <c r="C241" s="1">
-        <v>1.6568436429899291</v>
+        <v>1.684440568604394</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C241" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{96a21d00-d811-4c05-8ac4-2d5708526a0a}" enabled="0" method="" siteId="{96a21d00-d811-4c05-8ac4-2d5708526a0a}" removed="1"/>
+</clbl:labelList>
 </file>